--- a/src/newganmanager/resources/肤色代码示例.xlsx
+++ b/src/newganmanager/resources/肤色代码示例.xlsx
@@ -1,29 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="10620"/>
+    <workbookView windowWidth="25580" windowHeight="8620"/>
   </bookViews>
   <sheets>
     <sheet name="基础肤色代码0-10" sheetId="1" r:id="rId1"/>
     <sheet name="拓展肤色代码0-19" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -123,11 +110,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -146,17 +133,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -170,26 +149,47 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -201,16 +201,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,16 +240,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,43 +262,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,7 +286,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,7 +334,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -323,13 +382,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -341,13 +406,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -359,13 +430,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,43 +448,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -425,61 +466,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -508,35 +495,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -556,17 +521,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -586,6 +554,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -594,168 +592,157 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -785,9 +772,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -795,52 +779,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -883,7 +867,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="723900" y="708660"/>
+          <a:off x="735330" y="689610"/>
           <a:ext cx="845820" cy="1036320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -925,7 +909,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1783080" y="701040"/>
+          <a:off x="1814830" y="681990"/>
           <a:ext cx="922020" cy="1028700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -967,7 +951,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2819400" y="685800"/>
+          <a:off x="2871470" y="666750"/>
           <a:ext cx="1005840" cy="1082040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1009,7 +993,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3954780" y="762000"/>
+          <a:off x="4027170" y="742950"/>
           <a:ext cx="899160" cy="952500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1051,7 +1035,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="701040" y="1859280"/>
+          <a:off x="712470" y="1840230"/>
           <a:ext cx="914400" cy="982980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1093,7 +1077,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1828800" y="1866900"/>
+          <a:off x="1860550" y="1847850"/>
           <a:ext cx="838200" cy="975360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1135,7 +1119,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="701040" y="4130040"/>
+          <a:off x="712470" y="4110990"/>
           <a:ext cx="929640" cy="1021080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1177,7 +1161,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="678180" y="12131040"/>
+          <a:off x="689610" y="12111990"/>
           <a:ext cx="952500" cy="1028700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1219,7 +1203,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1775460" y="12123420"/>
+          <a:off x="1807210" y="12104370"/>
           <a:ext cx="853440" cy="998220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1261,7 +1245,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2880360" y="12115800"/>
+          <a:off x="2932430" y="12096750"/>
           <a:ext cx="868680" cy="1059180"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1303,7 +1287,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2880360" y="1836420"/>
+          <a:off x="2932430" y="1817370"/>
           <a:ext cx="891540" cy="967740"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1345,7 +1329,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3954780" y="1828800"/>
+          <a:off x="4027170" y="1809750"/>
           <a:ext cx="922020" cy="1051560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1387,7 +1371,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="716280" y="3032760"/>
+          <a:off x="727710" y="3013710"/>
           <a:ext cx="883920" cy="914400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1429,7 +1413,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5052060" y="693420"/>
+          <a:off x="5144770" y="674370"/>
           <a:ext cx="815340" cy="1028700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1471,7 +1455,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5036820" y="1866900"/>
+          <a:off x="5129530" y="1847850"/>
           <a:ext cx="876300" cy="1021080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1513,7 +1497,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1821180" y="4130040"/>
+          <a:off x="1852930" y="4110990"/>
           <a:ext cx="861060" cy="998220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1555,7 +1539,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2857500" y="4099560"/>
+          <a:off x="2909570" y="4080510"/>
           <a:ext cx="914400" cy="1074420"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1597,7 +1581,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1790700" y="3009900"/>
+          <a:off x="1822450" y="2990850"/>
           <a:ext cx="906780" cy="960120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1639,7 +1623,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2834640" y="2987040"/>
+          <a:off x="2886710" y="2967990"/>
           <a:ext cx="952500" cy="1013460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1681,7 +1665,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3962400" y="2994660"/>
+          <a:off x="4034790" y="2975610"/>
           <a:ext cx="899160" cy="975360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1723,7 +1707,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5006340" y="2956560"/>
+          <a:off x="5099050" y="2937510"/>
           <a:ext cx="960120" cy="1074420"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1765,7 +1749,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3931920" y="4122420"/>
+          <a:off x="4004310" y="4103370"/>
           <a:ext cx="922020" cy="1021080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1807,7 +1791,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5036820" y="4137660"/>
+          <a:off x="5129530" y="4118610"/>
           <a:ext cx="922020" cy="1005840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1849,7 +1833,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="678180" y="5265420"/>
+          <a:off x="689610" y="5246370"/>
           <a:ext cx="937260" cy="1043940"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1891,7 +1875,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1790700" y="5273040"/>
+          <a:off x="1822450" y="5253990"/>
           <a:ext cx="868680" cy="1036320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1933,7 +1917,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="708660" y="10995660"/>
+          <a:off x="720090" y="10976610"/>
           <a:ext cx="876300" cy="967740"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1975,7 +1959,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3909060" y="12131040"/>
+          <a:off x="3981450" y="12111990"/>
           <a:ext cx="982980" cy="998220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2017,7 +2001,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1775460" y="10995660"/>
+          <a:off x="1807210" y="10976610"/>
           <a:ext cx="899160" cy="998220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2059,7 +2043,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="693420" y="6400800"/>
+          <a:off x="704850" y="6381750"/>
           <a:ext cx="944880" cy="1051560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2101,7 +2085,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2880360" y="11010900"/>
+          <a:off x="2932430" y="10991850"/>
           <a:ext cx="906780" cy="952500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2143,7 +2127,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="739140" y="7543800"/>
+          <a:off x="750570" y="7524750"/>
           <a:ext cx="830580" cy="998220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2185,7 +2169,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1744980" y="6400800"/>
+          <a:off x="1776730" y="6381750"/>
           <a:ext cx="975360" cy="1059180"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2227,7 +2211,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1798320" y="7566660"/>
+          <a:off x="1830070" y="7547610"/>
           <a:ext cx="914400" cy="998220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2269,7 +2253,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3924300" y="10988040"/>
+          <a:off x="3996690" y="10968990"/>
           <a:ext cx="815340" cy="998220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2311,7 +2295,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2872740" y="6477000"/>
+          <a:off x="2924810" y="6457950"/>
           <a:ext cx="861060" cy="960120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2353,7 +2337,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="716280" y="9875520"/>
+          <a:off x="727710" y="9856470"/>
           <a:ext cx="830580" cy="937260"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2395,7 +2379,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3962400" y="6461760"/>
+          <a:off x="4034790" y="6442710"/>
           <a:ext cx="838200" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2437,7 +2421,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="800100" y="8679180"/>
+          <a:off x="811530" y="8660130"/>
           <a:ext cx="769620" cy="1051560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2479,7 +2463,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5074920" y="10995660"/>
+          <a:off x="5167630" y="10976610"/>
           <a:ext cx="845820" cy="1013460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2521,7 +2505,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4998720" y="12108180"/>
+          <a:off x="5091430" y="12089130"/>
           <a:ext cx="891540" cy="1066800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2563,7 +2547,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5074920" y="6408420"/>
+          <a:off x="5167630" y="6389370"/>
           <a:ext cx="861060" cy="1059180"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2605,7 +2589,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2834640" y="5288280"/>
+          <a:off x="2886710" y="5269230"/>
           <a:ext cx="853440" cy="990600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2647,7 +2631,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3947160" y="5288280"/>
+          <a:off x="4019550" y="5269230"/>
           <a:ext cx="883920" cy="998220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2689,7 +2673,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5044440" y="5295900"/>
+          <a:off x="5137150" y="5276850"/>
           <a:ext cx="845820" cy="1013460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2731,7 +2715,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1760220" y="8732520"/>
+          <a:off x="1791970" y="8713470"/>
           <a:ext cx="922020" cy="975360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2773,7 +2757,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2842260" y="8709660"/>
+          <a:off x="2894330" y="8690610"/>
           <a:ext cx="792480" cy="952500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2815,7 +2799,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3954780" y="8755380"/>
+          <a:off x="4027170" y="8736330"/>
           <a:ext cx="876300" cy="914400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2857,7 +2841,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5029200" y="8686800"/>
+          <a:off x="5121910" y="8667750"/>
           <a:ext cx="868680" cy="1028700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2899,7 +2883,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1798320" y="9875520"/>
+          <a:off x="1830070" y="9856470"/>
           <a:ext cx="883920" cy="944880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2941,7 +2925,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2857500" y="7543800"/>
+          <a:off x="2909570" y="7524750"/>
           <a:ext cx="876300" cy="1013460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2983,7 +2967,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3939540" y="7566660"/>
+          <a:off x="4011930" y="7547610"/>
           <a:ext cx="876300" cy="960120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3025,7 +3009,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5029200" y="7536180"/>
+          <a:off x="5121910" y="7517130"/>
           <a:ext cx="906780" cy="1013460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3072,7 +3056,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="731520" y="723900"/>
+          <a:off x="742950" y="704850"/>
           <a:ext cx="1493520" cy="601980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3114,7 +3098,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="693420" y="1455420"/>
+          <a:off x="704850" y="1436370"/>
           <a:ext cx="1539240" cy="609600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3156,7 +3140,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="678180" y="2225040"/>
+          <a:off x="689610" y="2205990"/>
           <a:ext cx="1600200" cy="655320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3198,7 +3182,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="701040" y="2994660"/>
+          <a:off x="712470" y="2975610"/>
           <a:ext cx="1539240" cy="624840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3240,7 +3224,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="693420" y="3749040"/>
+          <a:off x="704850" y="3729990"/>
           <a:ext cx="1546860" cy="632460"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3282,7 +3266,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="693420" y="4511040"/>
+          <a:off x="704850" y="4491990"/>
           <a:ext cx="1531620" cy="640080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3324,7 +3308,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="731520" y="5257800"/>
+          <a:off x="742950" y="5238750"/>
           <a:ext cx="1539240" cy="662940"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3366,7 +3350,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="739140" y="6019800"/>
+          <a:off x="750570" y="6000750"/>
           <a:ext cx="1516380" cy="670560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3408,7 +3392,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="723900" y="6789420"/>
+          <a:off x="735330" y="6770370"/>
           <a:ext cx="1508760" cy="685800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3450,7 +3434,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="716280" y="7559040"/>
+          <a:off x="727710" y="7539990"/>
           <a:ext cx="1524000" cy="617220"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3492,7 +3476,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="731520" y="8328660"/>
+          <a:off x="742950" y="8309610"/>
           <a:ext cx="1516380" cy="647700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3534,7 +3518,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="716280" y="9067800"/>
+          <a:off x="727710" y="9048750"/>
           <a:ext cx="1546860" cy="670560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3576,7 +3560,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="731520" y="9845040"/>
+          <a:off x="742950" y="9825990"/>
           <a:ext cx="1508760" cy="647700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3618,7 +3602,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="739140" y="10622280"/>
+          <a:off x="750570" y="10603230"/>
           <a:ext cx="1508760" cy="647700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3660,7 +3644,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="762000" y="11369040"/>
+          <a:off x="773430" y="11349990"/>
           <a:ext cx="1501140" cy="640080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3702,7 +3686,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="746760" y="12131040"/>
+          <a:off x="758190" y="12111990"/>
           <a:ext cx="1524000" cy="640080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3744,7 +3728,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="754380" y="12931140"/>
+          <a:off x="765810" y="12912090"/>
           <a:ext cx="1508760" cy="609600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3786,7 +3770,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="754380" y="13647420"/>
+          <a:off x="765810" y="13628370"/>
           <a:ext cx="1501140" cy="647700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3828,7 +3812,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="739140" y="14417040"/>
+          <a:off x="750570" y="14397990"/>
           <a:ext cx="1539240" cy="662940"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3870,7 +3854,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="762000" y="15171420"/>
+          <a:off x="773430" y="15152370"/>
           <a:ext cx="1493520" cy="640080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4138,14 +4122,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="6" width="15.7777777777778" customWidth="1"/>
-    <col min="7" max="7" width="20.7777777777778" customWidth="1"/>
+    <col min="2" max="6" width="15.7818181818182" customWidth="1"/>
+    <col min="7" max="7" width="20.7818181818182" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36.6" spans="1:7">
+    <row r="1" ht="35.5" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4163,11 +4147,11 @@
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5" t="s">
         <v>3</v>
       </c>
     </row>
@@ -4175,12 +4159,12 @@
       <c r="A3" s="7">
         <v>0</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4188,11 +4172,11 @@
       <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
       <c r="G4" s="8" t="s">
         <v>5</v>
       </c>
@@ -4201,12 +4185,12 @@
       <c r="A5" s="7">
         <v>2</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4214,12 +4198,12 @@
       <c r="A6" s="7">
         <v>3</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4227,12 +4211,12 @@
       <c r="A7" s="7">
         <v>4</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4240,12 +4224,12 @@
       <c r="A8" s="7">
         <v>5</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11" t="s">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4253,12 +4237,12 @@
       <c r="A9" s="7">
         <v>6</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -4266,12 +4250,12 @@
       <c r="A10" s="7">
         <v>7</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11" t="s">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4279,12 +4263,12 @@
       <c r="A11" s="7">
         <v>8</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4292,12 +4276,12 @@
       <c r="A12" s="7">
         <v>9</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11" t="s">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4305,12 +4289,12 @@
       <c r="A13" s="7">
         <v>10</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -4330,13 +4314,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="30.7777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.7777777777778" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.7818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7818181818182" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36.6" spans="1:3">
+    <row r="1" ht="35.5" spans="1:3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
